--- a/DataTables/Datas/battle.enemy_behavior.xlsx
+++ b/DataTables/Datas/battle.enemy_behavior.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R0079a42d77f94201"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R6dd6e9921733417d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -604,16 +604,100 @@
       </x:c>
     </x:row>
     <x:row r="8">
-      <x:c r="B8"/>
-      <x:c r="C8"/>
-      <x:c r="D8"/>
-      <x:c r="E8"/>
+      <x:c r="A8"/>
+      <x:c r="B8" t="n">
+        <x:v>7101</x:v>
+      </x:c>
+      <x:c r="C8" t="str">
+        <x:v>Buff</x:v>
+      </x:c>
+      <x:c r="D8" t="str">
+        <x:v>Self</x:v>
+      </x:c>
+      <x:c r="E8" t="n">
+        <x:v>4001</x:v>
+      </x:c>
+      <x:c r="F8" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G8" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H8" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="9">
-      <x:c r="B9"/>
-      <x:c r="C9"/>
-      <x:c r="D9"/>
-      <x:c r="E9"/>
+      <x:c r="A9"/>
+      <x:c r="B9" t="n">
+        <x:v>7102</x:v>
+      </x:c>
+      <x:c r="C9" t="str">
+        <x:v>Attack</x:v>
+      </x:c>
+      <x:c r="D9" t="str">
+        <x:v>Enemy</x:v>
+      </x:c>
+      <x:c r="E9" t="n">
+        <x:v>4004</x:v>
+      </x:c>
+      <x:c r="F9" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G9" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H9" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10"/>
+      <x:c r="B10" t="n">
+        <x:v>7201</x:v>
+      </x:c>
+      <x:c r="C10" t="str">
+        <x:v>Defend</x:v>
+      </x:c>
+      <x:c r="D10" t="str">
+        <x:v>Self</x:v>
+      </x:c>
+      <x:c r="E10" t="n">
+        <x:v>4003</x:v>
+      </x:c>
+      <x:c r="F10" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G10" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H10" t="n">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11"/>
+      <x:c r="B11" t="n">
+        <x:v>7202</x:v>
+      </x:c>
+      <x:c r="C11" t="str">
+        <x:v>Attack</x:v>
+      </x:c>
+      <x:c r="D11" t="str">
+        <x:v>Enemy</x:v>
+      </x:c>
+      <x:c r="E11" t="n">
+        <x:v>4004</x:v>
+      </x:c>
+      <x:c r="F11" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G11" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H11" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
